--- a/docs/oc-regiones/suministro-de-combustibles/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2230.42</v>
+        <v>2207.06</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2244.32</v>
+        <v>2220.81</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3179.45</v>
+        <v>3146.15</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3179.45</v>
+        <v>3146.15</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9297.879999999999</v>
+        <v>9200.51</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8229.16</v>
+        <v>8184.18</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3633.65</v>
+        <v>3613.79</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5343.61</v>
+        <v>5336.81</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2229.63</v>
+        <v>2226.79</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2351.19</v>
+        <v>2358.92</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3588.68</v>
+        <v>3605.39</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8549.77</v>
+        <v>8611.41</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4274.89</v>
+        <v>4267.3</v>
       </c>
     </row>
     <row r="15">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2229.63</v>
+        <v>2225.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1609-413-CM25</t>
+          <t>1609-412-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10687.21</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1609-412-CM25</t>
+          <t>1609-413-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5343.61</v>
+        <v>10670.65</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5343.61</v>
+        <v>5381.32</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5457.54</v>
+        <v>5387</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2277.17</v>
+        <v>2254.51</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2292.17</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5909.14</v>
+        <v>5887.96</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6003.3</v>
+        <v>5981.77</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>29289.55</v>
+        <v>29226.16</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2292.17</v>
+        <v>2282.56</v>
       </c>
     </row>
     <row r="26">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2292.17</v>
+        <v>2290.33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4589-595-CM25</t>
+          <t>2663-667-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2597.79</v>
+        <v>5482.28</v>
       </c>
     </row>
     <row r="28">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2597.79</v>
+        <v>2609.56</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2663-667-CM25</t>
+          <t>4589-595-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5457.54</v>
+        <v>2609.56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3617-259-CM25</t>
+          <t>1759-511-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.901.014-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XII REGION</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2292.17</v>
+        <v>2517.13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1759-511-CM25</t>
+          <t>3617-259-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.901.014-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XII REGION</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2510.47</v>
+        <v>2298.25</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2280.57</v>
+        <v>2277.37</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5457.54</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4038.58</v>
+        <v>4066.38</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3165.38</v>
+        <v>3192.43</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2292.17</v>
+        <v>2311.76</v>
       </c>
     </row>
     <row r="37">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>10915.09</v>
+        <v>11008.37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>638-224-CM25</t>
+          <t>764-421-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.824.000-2</t>
+          <t>60.511.120-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2277.34</v>
+        <v>3958.49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>764-421-CM25</t>
+          <t>638-224-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.511.120-3</t>
+          <t>61.824.000-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3916.48</v>
+        <v>2301.77</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2728.77</v>
+        <v>2763.84</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>7351.29</v>
+        <v>7391.5</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7094.81</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5656.33</v>
+        <v>5511.89</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6900.72</v>
+        <v>6766.13</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>14706.45</v>
+        <v>14362.42</v>
       </c>
     </row>
     <row r="46">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4130.35</v>
+        <v>4033.73</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1080089-2-CM26</t>
+          <t>1080094-1-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8823.870000000001</v>
+        <v>22301.02</v>
       </c>
     </row>
     <row r="48">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2375.66</v>
+        <v>2341.61</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1080094-1-CM26</t>
+          <t>1080089-2-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>22625.31</v>
+        <v>8697.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1080095-1-CM26</t>
+          <t>874750-12-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>5656.33</v>
+        <v>22338.13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>874750-12-CM26</t>
+          <t>1080095-1-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>22625.31</v>
+        <v>5584.53</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2375.66</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5656.33</v>
+        <v>5652.46</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2828.16</v>
+        <v>2826.23</v>
       </c>
     </row>
     <row r="55">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3959.43</v>
+        <v>3938.51</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1540-186-CM26</t>
+          <t>1057402-787-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2370</v>
+        <v>2383.26</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057402-787-CM26</t>
+          <t>1540-186-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2367.74</v>
+        <v>2385.53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>750-2-CM26</t>
+          <t>2019-1-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2019-1-CM26</t>
+          <t>750-2-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7428.17</v>
+        <v>7541.26</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>8484.49</v>
+        <v>8698.98</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5656.33</v>
+        <v>5824.45</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2375.66</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>8700.49</v>
+        <v>8663.809999999999</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>16240.92</v>
+        <v>16285.51</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.85</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>19334.43</v>
+        <v>19461.76</v>
       </c>
     </row>
     <row r="68">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>11600.66</v>
+        <v>11703.98</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2663-73-CM26</t>
+          <t>4052-13-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5800.33</v>
+        <v>11588.69</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4052-13-CM26</t>
+          <t>2663-73-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>11600.66</v>
+        <v>5794.35</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5800.33</v>
+        <v>5766.15</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>51042.9</v>
+        <v>50742.1</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>11600.66</v>
+        <v>11530.17</v>
       </c>
     </row>
     <row r="74">
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2552.14</v>
+        <v>2536.64</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1988-8-CM26</t>
+          <t>1988-7-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3480.2</v>
+        <v>2435.14</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1988-7-CM26</t>
+          <t>1988-8-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2422.6</v>
+        <v>3498.22</v>
       </c>
     </row>
     <row r="77">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2307.96</v>
+        <v>2317.06</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2663-107-CM26</t>
+          <t>1540-600-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>5495.15</v>
+        <v>8602.01</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1540-600-CM26</t>
+          <t>2663-107-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8462.530000000001</v>
+        <v>5585.72</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5495.15</v>
+        <v>5508.67</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>7761.35</v>
+        <v>7661.43</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2615.69</v>
+        <v>2663.12</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3269.61</v>
+        <v>3328.89</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3269.61</v>
+        <v>3328.89</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3297.09</v>
+        <v>3310.71</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5495.15</v>
+        <v>5431.71</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5495.15</v>
+        <v>5463.59</v>
       </c>
     </row>
     <row r="88">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2307.96</v>
+        <v>2293.18</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3637-87-CM26</t>
+          <t>1239966-109-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5841,17 +5841,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.251.500-5</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
+          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>26651.48</v>
+        <v>2258.31</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1239966-109-CM26</t>
+          <t>3637-87-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5902,17 +5902,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>69.251.500-5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2307.96</v>
+        <v>26078.07</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>4274.58</v>
+        <v>4190.28</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5568.63</v>
+        <v>5421.99</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>21160.81</v>
+        <v>20777.06</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3898.04</v>
+        <v>3827.35</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2335.49</v>
+        <v>2272.95</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7096.53</v>
+        <v>7084.66</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5568.63</v>
+        <v>5637.17</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>8352.950000000001</v>
+        <v>8461.959999999999</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>9281.059999999999</v>
+        <v>9402.17</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2711.65</v>
+        <v>2762.93</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>11137.27</v>
+        <v>11263.93</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2784.32</v>
+        <v>2809.4</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8909.82</v>
+        <v>8966.799999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>8575.700000000001</v>
+        <v>8630.549999999999</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2338.83</v>
+        <v>2353.79</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4343.53</v>
+        <v>4371.32</v>
       </c>
     </row>
     <row r="107">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>7239.22</v>
+        <v>7285.53</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2348-195-CM26</t>
+          <t>3704-110-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>15592.18</v>
+        <v>2901.69</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2348-200-CM26</t>
+          <t>1038-75-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7061,17 +7061,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,32 +7081,28 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>191168.9</v>
+        <v>5580.17</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1038-75-CM26</t>
+          <t>2348-195-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7131,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7161,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5568.63</v>
+        <v>15624.48</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3704-110-CM26</t>
+          <t>2348-200-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7187,17 +7183,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7215,14 +7211,18 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2895.69</v>
+        <v>191564.92</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2338.83</v>
+        <v>2328.78</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>6007.61</v>
+        <v>5925.93</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2617.98</v>
+        <v>2632.08</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>4456.14</v>
+        <v>4489.89</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>23156.02</v>
+        <v>23243.75</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2450.88</v>
+        <v>2460.16</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2360.12</v>
+        <v>2354.16</v>
       </c>
     </row>
     <row r="119">
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3342.1</v>
+        <v>3333.67</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3366-26-CM26</t>
+          <t>2663-259-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.101.010-9</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>42753.15</v>
+        <v>8889.780000000001</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2663-259-CM26</t>
+          <t>3366-26-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.101.010-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>42645.21</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2359.15</v>
+        <v>2381.56</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2785.09</v>
+        <v>2772.88</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2359.53</v>
+        <v>2367.35</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>9469.299999999999</v>
+        <v>9500.709999999999</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8940.65</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2469.12</v>
+        <v>2476.97</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>8855.59</v>
+        <v>8982.299999999999</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>22138.97</v>
+        <v>22398.67</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2379.94</v>
+        <v>2407.86</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3320.85</v>
+        <v>3295.65</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>11069.49</v>
+        <v>10882.46</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>3031.23</v>
+        <v>2988.21</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>6641.69</v>
+        <v>6547.43</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3119.31</v>
+        <v>3076.45</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>8855.59</v>
+        <v>8800.690000000001</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>7195.17</v>
+        <v>7227.84</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2767.37</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6641.69</v>
+        <v>6687.55</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2379.94</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2767.37</v>
+        <v>2760.05</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>55347.43</v>
+        <v>54610.19</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>12176.43</v>
+        <v>11996.03</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>9130.26</v>
+        <v>9165.9</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2309.42</v>
+        <v>2318.43</v>
       </c>
     </row>
     <row r="146">
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8679.24</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2348-296-CM26</t>
+          <t>2348-298-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>8056.11</v>
+        <v>12939.96</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2348-298-CM26</t>
+          <t>2348-296-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>12889.78</v>
+        <v>8087.47</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>10741.48</v>
+        <v>10687.07</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2309.42</v>
+        <v>2297.72</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2857.5</v>
+        <v>2876.13</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>6928.26</v>
+        <v>6944.15</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2308.85</v>
+        <v>2314.14</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>9882.17</v>
+        <v>9860.66</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8575.959999999999</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8493.200000000001</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,129 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2363.13</v>
+        <v>2378.94</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>3617-97-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>16404.02</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1490610-10-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>24489.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M159"/>
+  <dimension ref="A1:M174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1057402-37814-CM25</t>
+          <t>1965-30-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2207.06</v>
+        <v>4019.21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>958479-301-CM25</t>
+          <t>764-15-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.720-0</t>
+          <t>60.511.120-3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO CRISTINA CALDERON DE PUERTO WILLIAMS</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2220.81</v>
+        <v>2127.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4589-541-CM25</t>
+          <t>2663-122-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3146.15</v>
+        <v>5283.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4589-542-CM25</t>
+          <t>2663-186-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3146.15</v>
+        <v>5318.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3637-338-CM25</t>
+          <t>707427-29-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.251.500-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9200.51</v>
+        <v>2192.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1540-4334-CM25</t>
+          <t>1965-349-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8184.18</v>
+        <v>2240.98</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1776-89-CM25</t>
+          <t>1277-17-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.804.017-K</t>
+          <t>60.805.026-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE PUNTA ARENAS</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3613.79</v>
+        <v>2196.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2663-594-CM25</t>
+          <t>2663-292-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5336.81</v>
+        <v>5323.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1277-33-CM25</t>
+          <t>1540-1687-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.805.026-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Magalllanes y Antártica Chil</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2226.79</v>
+        <v>2178.97</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>707427-83-CM25</t>
+          <t>1776-59-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.804.017-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2358.92</v>
+        <v>2634.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5338-928-CM25</t>
+          <t>4589-396-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3605.39</v>
+        <v>3046.84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1038-284-CM25</t>
+          <t>1858-14-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8611.41</v>
+        <v>2150.41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1965-727-CM25</t>
+          <t>2663-453-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4267.3</v>
+        <v>5174.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1759-462-CM25</t>
+          <t>1540-2062-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.901.014-2</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XII REGION</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2225.68</v>
+        <v>6518.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1609-412-CM25</t>
+          <t>4890-250-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.972.500-k</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5335.33</v>
+        <v>2200.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1609-413-CM25</t>
+          <t>1057402-37814-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10670.65</v>
+        <v>2207.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3866-146-CM25</t>
+          <t>958479-301-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>61.980.720-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>HOSPITAL COMUNITARIO CRISTINA CALDERON DE PUERTO WILLIAMS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5381.32</v>
+        <v>2220.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2663-638-CM25</t>
+          <t>4589-541-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5387</v>
+        <v>3146.15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1540-6575-CM25</t>
+          <t>4589-542-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2254.51</v>
+        <v>3146.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>661-92-CM25</t>
+          <t>3637-338-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.802.012-6</t>
+          <t>69.251.500-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2283.95</v>
+        <v>9200.51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1540-6591-CM25</t>
+          <t>1540-4334-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5887.96</v>
+        <v>8184.18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3617-236-CM25</t>
+          <t>1776-89-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.804.017-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5981.77</v>
+        <v>3613.79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2348-1646-CM25</t>
+          <t>1277-33-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>60.805.026-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>Tesorería Regional de Magalllanes y Antártica Chil</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>29226.16</v>
+        <v>2226.79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1038-304-CM25</t>
+          <t>2663-594-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2282.56</v>
+        <v>5336.81</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1233613-3890-CM25</t>
+          <t>707427-83-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2290.33</v>
+        <v>2358.92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2663-667-CM25</t>
+          <t>5338-928-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>5482.28</v>
+        <v>3605.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4589-594-CM25</t>
+          <t>1038-284-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2609.56</v>
+        <v>8611.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4589-595-CM25</t>
+          <t>1759-462-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>60.901.014-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XII REGION</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2609.56</v>
+        <v>2225.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1759-511-CM25</t>
+          <t>1965-727-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.901.014-2</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XII REGION</t>
+          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2517.13</v>
+        <v>4267.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3617-259-CM25</t>
+          <t>1609-412-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2298.25</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3241-321-CM25</t>
+          <t>1609-413-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.102.028-7</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2277.37</v>
+        <v>10670.65</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3704-433-CM25</t>
+          <t>3866-146-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5464.54</v>
+        <v>5381.32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1038-340-CM25</t>
+          <t>2663-638-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4066.38</v>
+        <v>5387</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1965-791-CM25</t>
+          <t>1540-6575-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3192.43</v>
+        <v>2254.51</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1965-792-CM25</t>
+          <t>661-92-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.802.012-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>Ministerio de Vivienda y Urbanismo</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2311.76</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2099-636-CM25</t>
+          <t>1540-6591-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>11008.37</v>
+        <v>5887.96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>764-421-CM25</t>
+          <t>3617-236-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.511.120-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3958.49</v>
+        <v>5981.77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>638-224-CM25</t>
+          <t>2348-1646-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.824.000-2</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2301.77</v>
+        <v>29226.16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>709129-84-CM25</t>
+          <t>1038-304-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ministerio Publico</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2763.84</v>
+        <v>2282.56</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1162-181-CM25</t>
+          <t>1233613-3890-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>7391.5</v>
+        <v>2290.33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1490610-6-CM25</t>
+          <t>4589-594-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7133.61</v>
+        <v>2609.56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2663-3-CM26</t>
+          <t>2663-667-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5511.89</v>
+        <v>5482.28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3641-1-CM26</t>
+          <t>4589-595-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.251.500-5</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6766.13</v>
+        <v>2609.56</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1080094-2-CM26</t>
+          <t>1759-511-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>60.901.014-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XII REGION</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>14362.42</v>
+        <v>2517.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5338-3-CM26</t>
+          <t>3617-259-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4033.73</v>
+        <v>2298.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1080094-1-CM26</t>
+          <t>3241-321-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,27 +3269,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>61.102.028-7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>22301.02</v>
+        <v>2277.37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1080089-1-CM26</t>
+          <t>3704-433-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,27 +3330,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2341.61</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1080089-2-CM26</t>
+          <t>1038-340-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8697.4</v>
+        <v>4066.38</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>874750-12-CM26</t>
+          <t>2099-636-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,27 +3452,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>22338.13</v>
+        <v>11008.37</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1080095-1-CM26</t>
+          <t>1965-792-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,27 +3513,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>5584.53</v>
+        <v>2311.76</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3542-14-CM26</t>
+          <t>1965-791-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2378.96</v>
+        <v>3192.43</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2663-16-CM26</t>
+          <t>638-224-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.824.000-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5652.46</v>
+        <v>2301.77</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1239966-20-CM26</t>
+          <t>764-421-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,27 +3696,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>60.511.120-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2826.23</v>
+        <v>3958.49</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1687-2-CM26</t>
+          <t>709129-84-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>Ministerio Publico</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3938.51</v>
+        <v>2763.84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057402-787-CM26</t>
+          <t>1162-181-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2383.26</v>
+        <v>7391.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1540-186-CM26</t>
+          <t>1490610-6-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2385.53</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2019-1-CM26</t>
+          <t>2663-3-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2407.65</v>
+        <v>5511.89</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>750-2-CM26</t>
+          <t>3641-1-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.251.500-5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2407.65</v>
+        <v>6766.13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1038-5-CM26</t>
+          <t>5338-3-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7541.26</v>
+        <v>4033.73</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3617-8-CM26</t>
+          <t>1080094-2-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,22 +4128,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>8698.98</v>
+        <v>14362.42</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2663-37-CM26</t>
+          <t>1080094-1-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,22 +4189,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5824.45</v>
+        <v>22301.02</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>935-15-CM26</t>
+          <t>1080089-1-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,43 +4290,43 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2446.27</v>
+        <v>2341.61</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1540-373-CM26</t>
+          <t>1080089-2-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,43 +4351,43 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>8663.809999999999</v>
+        <v>8697.4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3617-17-CM26</t>
+          <t>1080095-1-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,43 +4412,43 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>16285.51</v>
+        <v>5584.53</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>517903-2-CM26</t>
+          <t>874750-12-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.114.000-2</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>EMDN-RMA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,28 +4473,28 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3511.85</v>
+        <v>22338.13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2348-91-CM26</t>
+          <t>3542-14-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,28 +4534,28 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>19461.76</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4060-5-CM26</t>
+          <t>2663-16-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,43 +4595,43 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>11703.98</v>
+        <v>5652.46</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4052-13-CM26</t>
+          <t>1239966-20-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,28 +4656,28 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>11588.69</v>
+        <v>2826.23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2663-73-CM26</t>
+          <t>1687-2-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,28 +4717,28 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>5794.35</v>
+        <v>3938.51</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3617-44-CM26</t>
+          <t>1057402-787-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,28 +4778,28 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5766.15</v>
+        <v>2383.26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1237328-48-CM26</t>
+          <t>1540-186-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,28 +4839,28 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>50742.1</v>
+        <v>2385.53</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1233613-242-CM26</t>
+          <t>2019-1-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,28 +4900,28 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>11530.17</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1536-42-CM26</t>
+          <t>750-2-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL F</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,28 +4961,28 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2536.64</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1988-7-CM26</t>
+          <t>1038-5-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>60.701.003-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,28 +5022,28 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2435.14</v>
+        <v>7541.26</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1988-8-CM26</t>
+          <t>3617-8-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.701.003-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,28 +5083,28 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3498.22</v>
+        <v>8698.98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3166-99-CM26</t>
+          <t>2663-37-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,28 +5144,28 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2317.06</v>
+        <v>5824.45</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1540-600-CM26</t>
+          <t>935-15-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>8602.01</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2663-107-CM26</t>
+          <t>1540-373-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5585.72</v>
+        <v>8663.809999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3866-33-CM26</t>
+          <t>3617-17-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,27 +5282,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5508.67</v>
+        <v>16285.51</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3704-45-CM26</t>
+          <t>517903-2-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>61.114.000-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>EMDN-RMA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>7661.43</v>
+        <v>3511.85</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4589-114-CM26</t>
+          <t>2348-91-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,27 +5404,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2663.12</v>
+        <v>19461.76</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4589-115-CM26</t>
+          <t>4060-5-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,27 +5465,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3328.89</v>
+        <v>11703.98</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4589-116-CM26</t>
+          <t>2663-73-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,27 +5526,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3328.89</v>
+        <v>5794.35</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5147-55-CM26</t>
+          <t>4052-13-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,27 +5587,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3310.71</v>
+        <v>11588.69</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2663-133-CM26</t>
+          <t>3617-44-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5431.71</v>
+        <v>5766.15</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>638-46-CM26</t>
+          <t>1237328-48-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.824.000-2</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5463.59</v>
+        <v>50742.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1536-73-CM26</t>
+          <t>1536-42-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2293.18</v>
+        <v>2536.64</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1239966-109-CM26</t>
+          <t>1233613-242-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,27 +5831,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2258.31</v>
+        <v>11530.17</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3637-87-CM26</t>
+          <t>1988-7-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.251.500-5</t>
+          <t>60.701.003-K</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>26078.07</v>
+        <v>2435.14</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5338-167-CM26</t>
+          <t>1988-8-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>60.701.003-K</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>4190.28</v>
+        <v>3498.22</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2663-169-CM26</t>
+          <t>3166-99-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>CENTRO DE ABASTECIMIENTO (M)</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5421.99</v>
+        <v>2317.06</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3641-17-CM26</t>
+          <t>1540-600-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.251.500-5</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>20777.06</v>
+        <v>8602.01</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1173441-9-CM26</t>
+          <t>2663-107-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.972.900-5</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Punta Arenas</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3827.35</v>
+        <v>5585.72</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057402-3903-CM26</t>
+          <t>3866-33-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,27 +6197,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2272.95</v>
+        <v>5508.67</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1038-59-CM26</t>
+          <t>3704-45-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7084.66</v>
+        <v>7661.43</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2663-183-CM26</t>
+          <t>4589-115-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,27 +6319,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5637.17</v>
+        <v>3328.89</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2348-170-CM26</t>
+          <t>4589-116-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6380,27 +6380,27 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>8461.959999999999</v>
+        <v>3328.89</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2348-169-CM26</t>
+          <t>4589-114-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,27 +6441,27 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>9402.17</v>
+        <v>2663.12</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3241-88-CM26</t>
+          <t>5147-55-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,27 +6502,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.102.028-7</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2762.93</v>
+        <v>3310.71</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3866-52-CM26</t>
+          <t>2663-133-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,27 +6563,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>11263.93</v>
+        <v>5431.71</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4589-177-CM26</t>
+          <t>638-46-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,27 +6624,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>61.824.000-2</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2809.4</v>
+        <v>5463.59</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2663-206-CM26</t>
+          <t>1536-73-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL F</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8966.799999999999</v>
+        <v>2293.18</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1540-1012-CM26</t>
+          <t>3637-87-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>69.251.500-5</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>8630.549999999999</v>
+        <v>26078.07</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1965-186-CM26</t>
+          <t>1239966-109-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,27 +6807,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2353.79</v>
+        <v>2258.31</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1965-187-CM26</t>
+          <t>5338-167-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4371.32</v>
+        <v>4190.28</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3704-103-CM26</t>
+          <t>2663-169-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>7285.53</v>
+        <v>5421.99</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3704-110-CM26</t>
+          <t>3641-17-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>69.251.500-5</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2901.69</v>
+        <v>20777.06</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1038-75-CM26</t>
+          <t>1173441-9-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.972.900-5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Centro de Educación y Trabajo Punta Arenas</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>5580.17</v>
+        <v>3827.35</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2348-195-CM26</t>
+          <t>1057402-3903-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>15624.48</v>
+        <v>2272.95</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2348-200-CM26</t>
+          <t>1038-59-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,22 +7178,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7211,24 +7211,20 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>191564.92</v>
+        <v>7084.66</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>764-84-CM26</t>
+          <t>2663-183-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7243,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7253,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.511.120-3</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7268,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7283,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2328.78</v>
+        <v>5637.17</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5338-248-CM26</t>
+          <t>2348-169-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7299,27 +7295,27 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7344,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>5925.93</v>
+        <v>9402.17</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>829-18-CM26</t>
+          <t>2348-170-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7360,12 +7356,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7375,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7390,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7405,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2632.08</v>
+        <v>8461.959999999999</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1776-38-CM26</t>
+          <t>3241-88-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7421,12 +7417,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7436,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>60.804.017-K</t>
+          <t>61.102.028-7</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE PUNTA ARENAS</t>
+          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7466,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>4489.89</v>
+        <v>2762.93</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1162-70-CM26</t>
+          <t>3866-52-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7482,12 +7478,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7497,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7512,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7527,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>23243.75</v>
+        <v>11263.93</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1239966-171-CM26</t>
+          <t>4589-177-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7543,12 +7539,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7558,12 +7554,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7588,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2460.16</v>
+        <v>2809.4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2074-13-CM26</t>
+          <t>2663-206-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7604,12 +7600,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7619,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.902.072-5</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación de Magallanes</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7649,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2354.16</v>
+        <v>8966.799999999999</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>764-95-CM26</t>
+          <t>3704-103-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7665,12 +7661,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7680,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>60.511.120-3</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7695,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7710,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3333.67</v>
+        <v>7285.53</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2663-259-CM26</t>
+          <t>1965-187-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7726,12 +7722,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7741,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7756,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7771,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>8889.780000000001</v>
+        <v>4371.32</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3366-26-CM26</t>
+          <t>1965-186-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7787,12 +7783,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7802,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.101.010-9</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7817,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7832,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>42645.21</v>
+        <v>2353.79</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1277-14-CM26</t>
+          <t>1540-1012-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7848,27 +7844,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>60.805.026-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Magalllanes y Antártica Chil</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7893,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2381.56</v>
+        <v>8630.549999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4589-239-CM26</t>
+          <t>2348-195-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7909,27 +7905,27 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7939,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7954,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2772.88</v>
+        <v>15624.48</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1057402-5571-CM26</t>
+          <t>2348-200-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7970,27 +7966,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8000,28 +7996,32 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2367.35</v>
+        <v>191564.92</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1540-1232-CM26</t>
+          <t>1038-75-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8076,13 +8076,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>9500.709999999999</v>
+        <v>5580.17</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2663-304-CM26</t>
+          <t>3704-110-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>8940.65</v>
+        <v>2901.69</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3617-78-CM26</t>
+          <t>764-84-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.511.120-3</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2476.97</v>
+        <v>2328.78</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2348-236-CM26</t>
+          <t>5338-248-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8214,27 +8214,27 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8259,13 +8259,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>8982.299999999999</v>
+        <v>5925.93</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1609-156-CM26</t>
+          <t>829-18-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8320,13 +8320,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>22398.67</v>
+        <v>2632.08</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1960-43-CM26</t>
+          <t>1776-38-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8336,27 +8336,27 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.804.017-K</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2407.86</v>
+        <v>4489.89</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1239966-233-CM26</t>
+          <t>1162-70-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8442,13 +8442,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3295.65</v>
+        <v>23243.75</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1038-124-CM26</t>
+          <t>1239966-171-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8458,27 +8458,27 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>10882.46</v>
+        <v>2460.16</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5338-329-CM26</t>
+          <t>3366-26-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.101.010-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8564,13 +8564,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2988.21</v>
+        <v>42645.21</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3617-83-CM26</t>
+          <t>2663-259-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8625,13 +8625,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>6547.43</v>
+        <v>8889.780000000001</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1288505-82-CM26</t>
+          <t>764-95-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.511.120-3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE MAGALLANES</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE MAGALLANES Y DE LA ANTÁRTICA CHILE</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3076.45</v>
+        <v>3333.67</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2663-355-CM26</t>
+          <t>2074-13-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>60.902.072-5</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>Departamento Provincial de Educación de Magallanes</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8747,13 +8747,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>8800.690000000001</v>
+        <v>2354.16</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3704-162-CM26</t>
+          <t>1277-14-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>60.805.026-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>Tesorería Regional de Magalllanes y Antártica Chil</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8808,13 +8808,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>7227.84</v>
+        <v>2381.56</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>732522-9-CM26</t>
+          <t>4589-239-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8824,27 +8824,27 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Geologia y Mineria</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2808.58</v>
+        <v>2772.88</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1965-333-CM26</t>
+          <t>1057402-5571-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8900,12 +8900,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8915,12 +8915,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6687.55</v>
+        <v>2367.35</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2019-26-CM26</t>
+          <t>1540-1232-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2387.3</v>
+        <v>9500.709999999999</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4589-298-CM26</t>
+          <t>3617-78-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9007,27 +9007,27 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2760.05</v>
+        <v>2476.97</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3638-302-CM26</t>
+          <t>2663-304-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9068,27 +9068,27 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.250.300-7</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE PORVENIR</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>54610.19</v>
+        <v>8940.65</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1233613-1314-CM26</t>
+          <t>2348-236-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9174,13 +9174,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>11996.03</v>
+        <v>8982.299999999999</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1540-1503-CM26</t>
+          <t>1960-43-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9190,27 +9190,27 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>9165.9</v>
+        <v>2407.86</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>638-96-CM26</t>
+          <t>1609-156-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.824.000-2</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2318.43</v>
+        <v>22398.67</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2663-411-CM26</t>
+          <t>1239966-233-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9312,27 +9312,27 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>8679.24</v>
+        <v>3295.65</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2348-298-CM26</t>
+          <t>1038-124-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9373,12 +9373,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>12939.96</v>
+        <v>10882.46</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2348-296-CM26</t>
+          <t>5338-329-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9434,12 +9434,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>8087.47</v>
+        <v>2988.21</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3866-78-CM26</t>
+          <t>3617-83-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9495,27 +9495,27 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>10687.07</v>
+        <v>6547.43</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1239966-281-CM26</t>
+          <t>1288505-82-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9556,27 +9556,27 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>DIRECCIÓN REGIONAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9601,13 +9601,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2297.72</v>
+        <v>3076.45</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3241-179-CM26</t>
+          <t>2663-355-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.102.028-7</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9662,13 +9662,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2876.13</v>
+        <v>8800.690000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1057402-7542-CM26</t>
+          <t>3704-162-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9678,27 +9678,27 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9723,13 +9723,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>6944.15</v>
+        <v>7227.84</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>855-111-CM26</t>
+          <t>732522-9-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9739,27 +9739,27 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Servicio Nacional de Geologia y Mineria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2314.14</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1540-1658-CM26</t>
+          <t>1965-333-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9845,13 +9845,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>9860.66</v>
+        <v>6687.55</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3704-213-CM26</t>
+          <t>2019-26-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9861,12 +9861,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9906,13 +9906,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>8575.959999999999</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2663-456-CM26</t>
+          <t>4589-298-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9922,12 +9922,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9967,13 +9967,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>8493.200000000001</v>
+        <v>2760.05</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>920802-95-CM26</t>
+          <t>3638-302-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9983,27 +9983,27 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>65.119.695-7</t>
+          <t>69.250.300-7</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Punta Arenas</t>
+          <t>I.MUNICIPALIDAD DE PORVENIR</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10028,13 +10028,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2378.94</v>
+        <v>54610.19</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3617-97-CM26</t>
+          <t>1233613-1314-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10044,12 +10044,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>16404.02</v>
+        <v>11996.03</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1490610-10-CM26</t>
+          <t>1540-1503-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10120,12 +10120,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10150,6 +10150,921 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
+        <v>9165.9</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>638-96-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>61.824.000-2</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>2318.43</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2663-411-CM26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>69.250.100-4</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>8679.24</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2348-298-CM26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>69.250.200-0</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>12939.96</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2348-296-CM26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>69.250.200-0</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>8087.47</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>3866-78-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>69.251.300-2</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>10687.07</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1239966-281-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>71.165.800-9</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>2297.72</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>3241-179-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>61.102.028-7</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>2876.13</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1057402-7542-CM26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>6944.15</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>855-111-CM26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>2314.14</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1540-1658-CM26</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>61.607.904-2</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>9860.66</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>3704-213-CM26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>69.254.400-5</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>8575.959999999999</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2663-456-CM26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>69.250.100-4</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>8493.200000000001</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>920802-95-CM26</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>65.119.695-7</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Zona de Bienestar Punta Arenas</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>2378.94</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>3617-97-CM26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>16404.02</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1490610-10-CM26</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n">
         <v>24489.71</v>
       </c>
     </row>
